--- a/rag/eval/results_new30/evaluation_metrics_fisher_new30.xlsx
+++ b/rag/eval/results_new30/evaluation_metrics_fisher_new30.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
         <v>0.2941966126471118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3595736376798033</v>
+        <v>0.4386611430059751</v>
       </c>
       <c r="J3" t="n">
         <v>0.8884120171673819</v>
@@ -599,7 +599,7 @@
         <v>0.08904462060164331</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1632484711030127</v>
+        <v>0.1908099012892357</v>
       </c>
       <c r="M3" t="n">
         <v>0.7666666666666667</v>
@@ -617,7 +617,7 @@
         <v>0.4235359986095568</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5044388904233663</v>
+        <v>0.4886953830110271</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         <v>0.03851341380755622</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1059118879707796</v>
+        <v>0.136126191828633</v>
       </c>
       <c r="J4" t="n">
         <v>0.9177489177489178</v>
@@ -657,7 +657,7 @@
         <v>0.00585928308662239</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02898575169012323</v>
+        <v>0.03952602503198622</v>
       </c>
       <c r="M4" t="n">
         <v>0.7851851851851852</v>
@@ -666,7 +666,7 @@
         <v>0.8355783137800722</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9185400915999676</v>
+        <v>0.8952624790500774</v>
       </c>
       <c r="P4" t="n">
         <v>0.846307385229541</v>
@@ -675,7 +675,7 @@
         <v>0.07083081731527124</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1255200181102397</v>
+        <v>0.1328077824661336</v>
       </c>
     </row>
     <row r="5">
@@ -715,7 +715,7 @@
         <v>0.4489877008788502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5487627455185947</v>
+        <v>0.6113773544187484</v>
       </c>
       <c r="M5" t="n">
         <v>0.725925925925926</v>
@@ -724,7 +724,7 @@
         <v>0.2329693195090835</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5125325029199838</v>
+        <v>0.3882821991818058</v>
       </c>
       <c r="P5" t="n">
         <v>0.7871485943775101</v>
@@ -806,7 +806,7 @@
         <v>0.1843526344432495</v>
       </c>
       <c r="I7" t="n">
-        <v>0.337979829812624</v>
+        <v>0.3950413595212489</v>
       </c>
       <c r="J7" t="n">
         <v>0.875</v>
@@ -815,7 +815,7 @@
         <v>0.2914771511575119</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4580355232475188</v>
+        <v>0.5465196584203349</v>
       </c>
       <c r="M7" t="n">
         <v>0.674074074074074</v>
@@ -824,7 +824,7 @@
         <v>0.001212149850067795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004444549450248581</v>
+        <v>0.006060749250338973</v>
       </c>
       <c r="P7" t="n">
         <v>0.7615062761506276</v>
@@ -833,7 +833,7 @@
         <v>0.02965208763324016</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06523459279312835</v>
+        <v>0.0741302190831004</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +864,7 @@
         <v>0.06388474037528354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1405464288256238</v>
+        <v>0.1597118509382088</v>
       </c>
       <c r="J8" t="n">
         <v>0.9570552147239264</v>
@@ -873,7 +873,7 @@
         <v>0.0001358538592277665</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001494392451505432</v>
+        <v>0.002037807888416497</v>
       </c>
       <c r="M8" t="n">
         <v>0.5777777777777777</v>
@@ -882,7 +882,7 @@
         <v>3.254588206680611e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.580047027348672e-07</v>
+        <v>4.881882310020916e-07</v>
       </c>
       <c r="P8" t="n">
         <v>0.7205542725173211</v>
@@ -891,7 +891,7 @@
         <v>0.0003556851287161614</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002942694585253531</v>
+        <v>0.004012765343527542</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>0.2802938024679246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3595736376798033</v>
+        <v>0.4386611430059751</v>
       </c>
       <c r="J9" t="n">
         <v>0.9051724137931034</v>
@@ -931,7 +931,7 @@
         <v>0.03131207263621193</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06888655979966624</v>
+        <v>0.07828018159052981</v>
       </c>
       <c r="M9" t="n">
         <v>0.7777777777777778</v>
@@ -940,7 +940,7 @@
         <v>0.598151417232868</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7310739543957276</v>
+        <v>0.6901747121917707</v>
       </c>
       <c r="P9" t="n">
         <v>0.8366533864541832</v>
@@ -949,7 +949,7 @@
         <v>0.4585808094757875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5044388904233663</v>
+        <v>0.4913365815812009</v>
       </c>
     </row>
     <row r="10">
@@ -1022,7 +1022,7 @@
         <v>0.4079243227111026</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4487167549822129</v>
+        <v>0.470681910820503</v>
       </c>
       <c r="J11" t="n">
         <v>0.8292682926829268</v>
@@ -1031,7 +1031,7 @@
         <v>0.5029383465204142</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5532321811724557</v>
+        <v>0.6113773544187484</v>
       </c>
       <c r="M11" t="n">
         <v>0.5037037037037037</v>
@@ -1040,7 +1040,7 @@
         <v>0.03779237333434917</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1039290266694602</v>
+        <v>0.0708607000019047</v>
       </c>
       <c r="P11" t="n">
         <v>0.6267281105990783</v>
@@ -1049,7 +1049,7 @@
         <v>0.07987637516106164</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1255200181102397</v>
+        <v>0.1331272919351027</v>
       </c>
     </row>
     <row r="12">
@@ -1080,7 +1080,7 @@
         <v>0.2713989199408965</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3595736376798033</v>
+        <v>0.4386611430059751</v>
       </c>
       <c r="J12" t="n">
         <v>0.7574257425742574</v>
@@ -1089,7 +1089,7 @@
         <v>0.3369063041206685</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4632461681659191</v>
+        <v>0.5615105068677808</v>
       </c>
       <c r="M12" t="n">
         <v>0.5666666666666667</v>
@@ -1098,7 +1098,7 @@
         <v>0.5414910279747216</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7310739543957276</v>
+        <v>0.6768637849684019</v>
       </c>
       <c r="P12" t="n">
         <v>0.6483050847457626</v>
@@ -1107,7 +1107,7 @@
         <v>0.2694073668193033</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3704351293765421</v>
+        <v>0.3367592085241292</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
         <v>0.01379025926589834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05056428397496057</v>
+        <v>0.06895129632949169</v>
       </c>
       <c r="J13" t="n">
         <v>0.8070866141732284</v>
@@ -1156,7 +1156,7 @@
         <v>7.066250536176908e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00038864377948973</v>
+        <v>0.0005299687902132681</v>
       </c>
       <c r="P13" t="n">
         <v>0.7824427480916031</v>
@@ -1165,7 +1165,7 @@
         <v>0.0005350353791370056</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002942694585253531</v>
+        <v>0.004012765343527542</v>
       </c>
     </row>
     <row r="14">
@@ -1196,7 +1196,7 @@
         <v>0.003884344984706906</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04272779483177596</v>
+        <v>0.05826517477060358</v>
       </c>
       <c r="J14" t="n">
         <v>0.7343173431734318</v>
@@ -1205,7 +1205,7 @@
         <v>0.007905205006397244</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02898575169012323</v>
+        <v>0.03952602503198622</v>
       </c>
       <c r="M14" t="n">
         <v>0.737037037037037</v>
@@ -1214,7 +1214,7 @@
         <v>0.3675171092021381</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6737813668705867</v>
+        <v>0.5512756638032072</v>
       </c>
       <c r="P14" t="n">
         <v>0.7356746765249538</v>
@@ -1223,7 +1223,7 @@
         <v>0.01088120654820858</v>
       </c>
       <c r="R14" t="n">
-        <v>0.03989775734343146</v>
+        <v>0.04486713294800101</v>
       </c>
     </row>
     <row r="15">
@@ -1254,7 +1254,7 @@
         <v>0.0112938125830885</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05056428397496057</v>
+        <v>0.06895129632949169</v>
       </c>
       <c r="J15" t="n">
         <v>0.7444444444444445</v>
@@ -1263,7 +1263,7 @@
         <v>0.01824495780244653</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05017363395672794</v>
+        <v>0.06841859175917447</v>
       </c>
       <c r="M15" t="n">
         <v>0.7444444444444445</v>
@@ -1272,7 +1272,7 @@
         <v>0.4811576238812952</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7310739543957276</v>
+        <v>0.6561240325654025</v>
       </c>
       <c r="P15" t="n">
         <v>0.7444444444444445</v>
@@ -1281,7 +1281,239 @@
         <v>0.02782408359658493</v>
       </c>
       <c r="R15" t="n">
-        <v>0.06523459279312835</v>
+        <v>0.0741302190831004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>480</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B BM25 RAG</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>194</v>
+      </c>
+      <c r="D16" t="n">
+        <v>178</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" t="n">
+        <v>76</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3854995794965347</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.470681910820503</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8584070796460177</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.529860373829582</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6113773544187484</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7185185185185186</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.03429763197812916</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0708607000019047</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.7822580645161291</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1592132843520616</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2388199265280924</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>480</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B Semantic RAG</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>188</v>
+      </c>
+      <c r="D17" t="n">
+        <v>169</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F17" t="n">
+        <v>82</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.74375</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.045375397276211</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.136126191828633</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8209606986899564</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7173831614461206</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7686248158351292</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6962962962962963</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.007304093357815778</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.01826023339453945</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7535070140280561</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.0119645687861336</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.04486713294800101</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>480</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B BM25 RAG</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>196</v>
+      </c>
+      <c r="D18" t="n">
+        <v>130</v>
+      </c>
+      <c r="E18" t="n">
+        <v>80</v>
+      </c>
+      <c r="F18" t="n">
+        <v>74</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6791666666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7812139271061912</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8370149218994906</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7101449275362319</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.02514040107426896</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.07542120322280689</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.725925925925926</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.00195386859918794</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.007327007246954776</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.7179487179487181</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2429307419903806</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3312691936232462</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>480</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B Semantic RAG</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>195</v>
+      </c>
+      <c r="D19" t="n">
+        <v>151</v>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>75</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7208333333333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3216848382043818</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4386611430059751</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7677165354330708</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4243596532873908</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6113773544187484</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.002685230995534966</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.008055692986604898</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.7442748091603052</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.03505381724051131</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.07511532265823853</v>
       </c>
     </row>
   </sheetData>

--- a/rag/eval/results_new30/evaluation_metrics_fisher_new30.xlsx
+++ b/rag/eval/results_new30/evaluation_metrics_fisher_new30.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D2" t="n">
         <v>168</v>
@@ -539,25 +539,25 @@
         <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.7875</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8326693227091634</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.774074074074074</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.8023032629558541</v>
+        <v>0.8045977011494253</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D3" t="n">
         <v>184</v>
@@ -581,43 +581,43 @@
         <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8145833333333333</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2941966126471118</v>
+        <v>0.2922956676040325</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4386611430059751</v>
+        <v>0.3985850012782262</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8884120171673819</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08904462060164331</v>
+        <v>0.08912330551409089</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1908099012892357</v>
+        <v>0.1909785118159091</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7703703703703704</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9185400915999676</v>
+        <v>0.9180742804771295</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9185400915999676</v>
+        <v>0.9180742804771295</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8230616302186879</v>
+        <v>0.8253968253968255</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4235359986095568</v>
+        <v>0.4217239375072824</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4886953830110271</v>
+        <v>0.4866045432776336</v>
       </c>
     </row>
     <row r="4">
@@ -645,37 +645,37 @@
         <v>0.8395833333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03851341380755622</v>
+        <v>0.04651868366841749</v>
       </c>
       <c r="I4" t="n">
-        <v>0.136126191828633</v>
+        <v>0.1597118509382088</v>
       </c>
       <c r="J4" t="n">
         <v>0.9177489177489178</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00585928308662239</v>
+        <v>0.005923902799465372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03952602503198622</v>
+        <v>0.03967381711339133</v>
       </c>
       <c r="M4" t="n">
         <v>0.7851851851851852</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8355783137800722</v>
+        <v>0.9170983094689434</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8952624790500774</v>
+        <v>0.9180742804771295</v>
       </c>
       <c r="P4" t="n">
         <v>0.846307385229541</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07083081731527124</v>
+        <v>0.08419295603379243</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1328077824661336</v>
+        <v>0.1403215933896541</v>
       </c>
     </row>
     <row r="5">
@@ -703,37 +703,37 @@
         <v>0.7791666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8757378657693639</v>
+        <v>0.814232107199506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8757378657693639</v>
+        <v>0.8348480186047937</v>
       </c>
       <c r="J5" t="n">
         <v>0.8596491228070176</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4489877008788502</v>
+        <v>0.4497285229107036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6113773544187484</v>
+        <v>0.6104783160818612</v>
       </c>
       <c r="M5" t="n">
         <v>0.725925925925926</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2329693195090835</v>
+        <v>0.195155531875494</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3882821991818058</v>
+        <v>0.3252592197924901</v>
       </c>
       <c r="P5" t="n">
         <v>0.7871485943775101</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5871252547276211</v>
+        <v>0.5341028562482713</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5871252547276211</v>
+        <v>0.5341028562482713</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
         <v>0.001212149850067795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006060749250338973</v>
+        <v>0.005279684965026082</v>
       </c>
       <c r="P7" t="n">
         <v>0.7615062761506276</v>
@@ -833,7 +833,7 @@
         <v>0.02965208763324016</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0741302190831004</v>
+        <v>0.06354018778551464</v>
       </c>
     </row>
     <row r="8">
@@ -891,7 +891,7 @@
         <v>0.0003556851287161614</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004012765343527542</v>
+        <v>0.002667638465371211</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>0.2802938024679246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4386611430059751</v>
+        <v>0.3985850012782262</v>
       </c>
       <c r="J9" t="n">
         <v>0.9051724137931034</v>
@@ -931,7 +931,7 @@
         <v>0.03131207263621193</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07828018159052981</v>
+        <v>0.08085619675497215</v>
       </c>
       <c r="M9" t="n">
         <v>0.7777777777777778</v>
@@ -1022,7 +1022,7 @@
         <v>0.4079243227111026</v>
       </c>
       <c r="I11" t="n">
-        <v>0.470681910820503</v>
+        <v>0.4954017505833005</v>
       </c>
       <c r="J11" t="n">
         <v>0.8292682926829268</v>
@@ -1031,7 +1031,7 @@
         <v>0.5029383465204142</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6113773544187484</v>
+        <v>0.6104783160818612</v>
       </c>
       <c r="M11" t="n">
         <v>0.5037037037037037</v>
@@ -1040,7 +1040,7 @@
         <v>0.03779237333434917</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0708607000019047</v>
+        <v>0.08098365714503394</v>
       </c>
       <c r="P11" t="n">
         <v>0.6267281105990783</v>
@@ -1049,7 +1049,7 @@
         <v>0.07987637516106164</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1331272919351027</v>
+        <v>0.1403215933896541</v>
       </c>
     </row>
     <row r="12">
@@ -1080,7 +1080,7 @@
         <v>0.2713989199408965</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4386611430059751</v>
+        <v>0.3985850012782262</v>
       </c>
       <c r="J12" t="n">
         <v>0.7574257425742574</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D13" t="n">
         <v>161</v>
@@ -1129,43 +1129,43 @@
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7625</v>
+        <v>0.7645833333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01379025926589834</v>
+        <v>0.01113891254302427</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06895129632949169</v>
+        <v>0.05569456271512133</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8070866141732284</v>
+        <v>0.807843137254902</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9055442562942386</v>
+        <v>0.9054381603048391</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9055442562942386</v>
+        <v>0.9054381603048391</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.762962962962963</v>
       </c>
       <c r="N13" t="n">
-        <v>7.066250536176908e-05</v>
+        <v>4.629325639763372e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0005299687902132681</v>
+        <v>0.0003471994229822529</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7824427480916031</v>
+        <v>0.7847619047619048</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0005350353791370056</v>
+        <v>0.0003130287739449427</v>
       </c>
       <c r="R13" t="n">
-        <v>0.004012765343527542</v>
+        <v>0.002667638465371211</v>
       </c>
     </row>
     <row r="14">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D14" t="n">
         <v>138</v>
@@ -1187,43 +1187,43 @@
         <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7020833333333333</v>
+        <v>0.7041666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003884344984706906</v>
+        <v>0.003788679703117095</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05826517477060358</v>
+        <v>0.05569456271512133</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7343173431734318</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007905205006397244</v>
+        <v>0.007934763422678267</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03952602503198622</v>
+        <v>0.03967381711339133</v>
       </c>
       <c r="M14" t="n">
-        <v>0.737037037037037</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3675171092021381</v>
+        <v>0.3650294799962009</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5512756638032072</v>
+        <v>0.5475442199943015</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7356746765249538</v>
+        <v>0.7380073800738007</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01088120654820858</v>
+        <v>0.01066517435405147</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04486713294800101</v>
+        <v>0.05332587177025735</v>
       </c>
     </row>
     <row r="15">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D15" t="n">
         <v>141</v>
@@ -1245,43 +1245,43 @@
         <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7125</v>
+        <v>0.7145833333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0112938125830885</v>
+        <v>0.01106701417239832</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06895129632949169</v>
+        <v>0.05569456271512133</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7453874538745388</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01824495780244653</v>
+        <v>0.01830511178854805</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06841859175917447</v>
+        <v>0.06864416920705517</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4811576238812952</v>
+        <v>0.4788229872473344</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6561240325654025</v>
+        <v>0.6529404371554559</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7467652495378928</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.02782408359658493</v>
+        <v>0.02739562111858774</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0741302190831004</v>
+        <v>0.06354018778551464</v>
       </c>
     </row>
     <row r="16">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D16" t="n">
         <v>178</v>
@@ -1303,43 +1303,43 @@
         <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="n">
-        <v>0.775</v>
+        <v>0.7770833333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3854995794965347</v>
+        <v>0.4293481838388605</v>
       </c>
       <c r="I16" t="n">
-        <v>0.470681910820503</v>
+        <v>0.4954017505833005</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8584070796460177</v>
+        <v>0.8590308370044053</v>
       </c>
       <c r="K16" t="n">
-        <v>0.529860373829582</v>
+        <v>0.5290812072709464</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6113773544187484</v>
+        <v>0.6104783160818612</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7185185185185186</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03429763197812916</v>
+        <v>0.04329826876131074</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0708607000019047</v>
+        <v>0.08118425392745764</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7822580645161291</v>
+        <v>0.784708249496982</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1592132843520616</v>
+        <v>0.1834241405671746</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2388199265280924</v>
+        <v>0.2751362108507619</v>
       </c>
     </row>
     <row r="17">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D17" t="n">
         <v>169</v>
@@ -1361,43 +1361,43 @@
         <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>0.74375</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>0.045375397276211</v>
+        <v>0.05395773354592306</v>
       </c>
       <c r="I17" t="n">
-        <v>0.136126191828633</v>
+        <v>0.1597118509382088</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8209606986899564</v>
+        <v>0.8217391304347826</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7173831614461206</v>
+        <v>0.7175533778009182</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7686248158351292</v>
+        <v>0.7688071905009838</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6962962962962963</v>
+        <v>0.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.007304093357815778</v>
+        <v>0.009618768562174241</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01826023339453945</v>
+        <v>0.0240469214054356</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7535070140280561</v>
+        <v>0.7559999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0119645687861336</v>
+        <v>0.01784601522787703</v>
       </c>
       <c r="R17" t="n">
-        <v>0.04486713294800101</v>
+        <v>0.06354018778551464</v>
       </c>
     </row>
     <row r="18">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D18" t="n">
         <v>130</v>
@@ -1419,43 +1419,43 @@
         <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6791666666666667</v>
+        <v>0.68125</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7812139271061912</v>
+        <v>0.8348480186047937</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8370149218994906</v>
+        <v>0.8348480186047937</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7101449275362319</v>
+        <v>0.7111913357400722</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02514040107426896</v>
+        <v>0.03234247870198886</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07542120322280689</v>
+        <v>0.08085619675497215</v>
       </c>
       <c r="M18" t="n">
-        <v>0.725925925925926</v>
+        <v>0.7296296296296296</v>
       </c>
       <c r="N18" t="n">
-        <v>0.00195386859918794</v>
+        <v>0.001407915990673622</v>
       </c>
       <c r="O18" t="n">
-        <v>0.007327007246954776</v>
+        <v>0.005279684965026082</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7179487179487181</v>
+        <v>0.720292504570384</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2429307419903806</v>
+        <v>0.215698956555618</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3312691936232462</v>
+        <v>0.294134940757661</v>
       </c>
     </row>
     <row r="19">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D19" t="n">
         <v>151</v>
@@ -1477,43 +1477,43 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7208333333333333</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3216848382043818</v>
+        <v>0.287823506642816</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4386611430059751</v>
+        <v>0.3985850012782262</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7677165354330708</v>
+        <v>0.7686274509803922</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4243596532873908</v>
+        <v>0.4251853916814302</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6113773544187484</v>
+        <v>0.6104783160818612</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.725925925925926</v>
       </c>
       <c r="N19" t="n">
-        <v>0.002685230995534966</v>
+        <v>0.00195386859918794</v>
       </c>
       <c r="O19" t="n">
-        <v>0.008055692986604898</v>
+        <v>0.005861605797563821</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7442748091603052</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.03505381724051131</v>
+        <v>0.02910865132719805</v>
       </c>
       <c r="R19" t="n">
-        <v>0.07511532265823853</v>
+        <v>0.06354018778551464</v>
       </c>
     </row>
   </sheetData>

--- a/rag/eval/results_new30/evaluation_metrics_fisher_new30.xlsx
+++ b/rag/eval/results_new30/evaluation_metrics_fisher_new30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
         <v>0.2922956676040325</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3985850012782262</v>
+        <v>0.350754801124839</v>
       </c>
       <c r="J3" t="n">
         <v>0.8888888888888888</v>
@@ -599,7 +599,7 @@
         <v>0.08912330551409089</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1909785118159091</v>
+        <v>0.2138959332338182</v>
       </c>
       <c r="M3" t="n">
         <v>0.7703703703703704</v>
@@ -617,7 +617,7 @@
         <v>0.4217239375072824</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4866045432776336</v>
+        <v>0.5002699739735864</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         <v>0.04651868366841749</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1597118509382088</v>
+        <v>0.1533233769006805</v>
       </c>
       <c r="J4" t="n">
         <v>0.9177489177489178</v>
@@ -657,7 +657,7 @@
         <v>0.005923902799465372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03967381711339133</v>
+        <v>0.03554341679679224</v>
       </c>
       <c r="M4" t="n">
         <v>0.7851851851851852</v>
@@ -675,7 +675,7 @@
         <v>0.08419295603379243</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1403215933896541</v>
+        <v>0.1262894340506887</v>
       </c>
     </row>
     <row r="5">
@@ -706,7 +706,7 @@
         <v>0.814232107199506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8348480186047937</v>
+        <v>0.8142321071995061</v>
       </c>
       <c r="J5" t="n">
         <v>0.8596491228070176</v>
@@ -715,7 +715,7 @@
         <v>0.4497285229107036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6104783160818612</v>
+        <v>0.5996380305476049</v>
       </c>
       <c r="M5" t="n">
         <v>0.725925925925926</v>
@@ -724,7 +724,7 @@
         <v>0.195155531875494</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3252592197924901</v>
+        <v>0.3345523403579898</v>
       </c>
       <c r="P5" t="n">
         <v>0.7871485943775101</v>
@@ -806,7 +806,7 @@
         <v>0.1843526344432495</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3950413595212489</v>
+        <v>0.350754801124839</v>
       </c>
       <c r="J7" t="n">
         <v>0.875</v>
@@ -815,7 +815,7 @@
         <v>0.2914771511575119</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5465196584203349</v>
+        <v>0.5775536642068602</v>
       </c>
       <c r="M7" t="n">
         <v>0.674074074074074</v>
@@ -824,7 +824,7 @@
         <v>0.001212149850067795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005279684965026082</v>
+        <v>0.004848599400271179</v>
       </c>
       <c r="P7" t="n">
         <v>0.7615062761506276</v>
@@ -833,7 +833,7 @@
         <v>0.02965208763324016</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06354018778551464</v>
+        <v>0.05930417526648032</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +864,7 @@
         <v>0.06388474037528354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1597118509382088</v>
+        <v>0.1533233769006805</v>
       </c>
       <c r="J8" t="n">
         <v>0.9570552147239264</v>
@@ -873,7 +873,7 @@
         <v>0.0001358538592277665</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002037807888416497</v>
+        <v>0.001630246310733198</v>
       </c>
       <c r="M8" t="n">
         <v>0.5777777777777777</v>
@@ -882,7 +882,7 @@
         <v>3.254588206680611e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.881882310020916e-07</v>
+        <v>3.905505848016733e-07</v>
       </c>
       <c r="P8" t="n">
         <v>0.7205542725173211</v>
@@ -891,7 +891,7 @@
         <v>0.0003556851287161614</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002667638465371211</v>
+        <v>0.002134110772296968</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>0.2802938024679246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3985850012782262</v>
+        <v>0.350754801124839</v>
       </c>
       <c r="J9" t="n">
         <v>0.9051724137931034</v>
@@ -931,7 +931,7 @@
         <v>0.03131207263621193</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08085619675497215</v>
+        <v>0.09393621790863578</v>
       </c>
       <c r="M9" t="n">
         <v>0.7777777777777778</v>
@@ -940,7 +940,7 @@
         <v>0.598151417232868</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6901747121917707</v>
+        <v>0.7177817006794417</v>
       </c>
       <c r="P9" t="n">
         <v>0.8366533864541832</v>
@@ -949,7 +949,7 @@
         <v>0.4585808094757875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4913365815812009</v>
+        <v>0.5002699739735864</v>
       </c>
     </row>
     <row r="10">
@@ -1022,7 +1022,7 @@
         <v>0.4079243227111026</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4954017505833005</v>
+        <v>0.4450083520484755</v>
       </c>
       <c r="J11" t="n">
         <v>0.8292682926829268</v>
@@ -1031,7 +1031,7 @@
         <v>0.5029383465204142</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6104783160818612</v>
+        <v>0.6035260158244971</v>
       </c>
       <c r="M11" t="n">
         <v>0.5037037037037037</v>
@@ -1040,7 +1040,7 @@
         <v>0.03779237333434917</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08098365714503394</v>
+        <v>0.07558474666869834</v>
       </c>
       <c r="P11" t="n">
         <v>0.6267281105990783</v>
@@ -1049,7 +1049,7 @@
         <v>0.07987637516106164</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1403215933896541</v>
+        <v>0.1262894340506887</v>
       </c>
     </row>
     <row r="12">
@@ -1080,7 +1080,7 @@
         <v>0.2713989199408965</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3985850012782262</v>
+        <v>0.350754801124839</v>
       </c>
       <c r="J12" t="n">
         <v>0.7574257425742574</v>
@@ -1089,7 +1089,7 @@
         <v>0.3369063041206685</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5615105068677808</v>
+        <v>0.5775536642068602</v>
       </c>
       <c r="M12" t="n">
         <v>0.5666666666666667</v>
@@ -1098,7 +1098,7 @@
         <v>0.5414910279747216</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6768637849684019</v>
+        <v>0.7177817006794417</v>
       </c>
       <c r="P12" t="n">
         <v>0.6483050847457626</v>
@@ -1107,7 +1107,7 @@
         <v>0.2694073668193033</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3367592085241292</v>
+        <v>0.3592098224257378</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
         <v>0.01113891254302427</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05569456271512133</v>
+        <v>0.06683347525814561</v>
       </c>
       <c r="J13" t="n">
         <v>0.807843137254902</v>
@@ -1147,7 +1147,7 @@
         <v>0.9054381603048391</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9054381603048391</v>
+        <v>0.9054381603048393</v>
       </c>
       <c r="M13" t="n">
         <v>0.762962962962963</v>
@@ -1156,7 +1156,7 @@
         <v>4.629325639763372e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0003471994229822529</v>
+        <v>0.0002777595383858023</v>
       </c>
       <c r="P13" t="n">
         <v>0.7847619047619048</v>
@@ -1165,7 +1165,7 @@
         <v>0.0003130287739449427</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002667638465371211</v>
+        <v>0.002134110772296968</v>
       </c>
     </row>
     <row r="14">
@@ -1174,56 +1174,56 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-4o BM25 RAG</t>
+          <t>GPT-4o RAG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D14" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7041666666666667</v>
+        <v>0.7145833333333333</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003788679703117095</v>
+        <v>0.01106701417239832</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05569456271512133</v>
+        <v>0.06683347525814561</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.7453874538745388</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007934763422678267</v>
+        <v>0.01830511178854805</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03967381711339133</v>
+        <v>0.07322044715419218</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3650294799962009</v>
+        <v>0.4788229872473344</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5475442199943015</v>
+        <v>0.7177817006794417</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7380073800738007</v>
+        <v>0.7467652495378928</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01066517435405147</v>
+        <v>0.02739562111858774</v>
       </c>
       <c r="R14" t="n">
-        <v>0.05332587177025735</v>
+        <v>0.05930417526648032</v>
       </c>
     </row>
     <row r="15">
@@ -1232,56 +1232,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-4o Semantic RAG</t>
+          <t>Llama3.1-70B RAG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D15" t="n">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7145833333333333</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01106701417239832</v>
+        <v>0.05395773354592306</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05569456271512133</v>
+        <v>0.1533233769006805</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7453874538745388</v>
+        <v>0.8217391304347826</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01830511178854805</v>
+        <v>0.7175533778009182</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06864416920705517</v>
+        <v>0.7827855030555472</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7481481481481481</v>
+        <v>0.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4788229872473344</v>
+        <v>0.009618768562174241</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6529404371554559</v>
+        <v>0.02308504454921818</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7467652495378928</v>
+        <v>0.7559999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.02739562111858774</v>
+        <v>0.01784601522787703</v>
       </c>
       <c r="R15" t="n">
-        <v>0.06354018778551464</v>
+        <v>0.05930417526648032</v>
       </c>
     </row>
     <row r="16">
@@ -1290,230 +1290,56 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Llama3.1-70B BM25 RAG</t>
+          <t>Llama3.1-8B RAG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D16" t="n">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7770833333333333</v>
+        <v>0.7229166666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4293481838388605</v>
+        <v>0.287823506642816</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4954017505833005</v>
+        <v>0.350754801124839</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8590308370044053</v>
+        <v>0.7686274509803922</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5290812072709464</v>
+        <v>0.4251853916814302</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6104783160818612</v>
+        <v>0.5996380305476049</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.725925925925926</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04329826876131074</v>
+        <v>0.00195386859918794</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08118425392745764</v>
+        <v>0.005861605797563821</v>
       </c>
       <c r="P16" t="n">
-        <v>0.784708249496982</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1834241405671746</v>
+        <v>0.02910865132719805</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2751362108507619</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>480</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B Semantic RAG</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>189</v>
-      </c>
-      <c r="D17" t="n">
-        <v>169</v>
-      </c>
-      <c r="E17" t="n">
-        <v>41</v>
-      </c>
-      <c r="F17" t="n">
-        <v>81</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.7458333333333333</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.05395773354592306</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1597118509382088</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8217391304347826</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7175533778009182</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.7688071905009838</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.009618768562174241</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.0240469214054356</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.7559999999999999</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.01784601522787703</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.06354018778551464</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>480</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B BM25 RAG</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>197</v>
-      </c>
-      <c r="D18" t="n">
-        <v>130</v>
-      </c>
-      <c r="E18" t="n">
-        <v>80</v>
-      </c>
-      <c r="F18" t="n">
-        <v>73</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.68125</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.8348480186047937</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.8348480186047937</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.7111913357400722</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.03234247870198886</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.08085619675497215</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7296296296296296</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.001407915990673622</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.005279684965026082</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.720292504570384</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.215698956555618</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.294134940757661</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>480</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B Semantic RAG</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>196</v>
-      </c>
-      <c r="D19" t="n">
-        <v>151</v>
-      </c>
-      <c r="E19" t="n">
-        <v>59</v>
-      </c>
-      <c r="F19" t="n">
-        <v>74</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.7229166666666667</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.287823506642816</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.3985850012782262</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.7686274509803922</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.4251853916814302</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.6104783160818612</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.725925925925926</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.00195386859918794</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.005861605797563821</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.7466666666666667</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.02910865132719805</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.06354018778551464</v>
+        <v>0.05930417526648032</v>
       </c>
     </row>
   </sheetData>
